--- a/FSD_Crossdock_Upload_Batch.xlsx
+++ b/FSD_Crossdock_Upload_Batch.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>0.1 (Draft)</t>
+          <t xml:space="preserve">0.2 (Draft)</t>
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
       <c r="C8" s="6" t="n"/>
@@ -728,6 +728,23 @@
       <c r="C19" s="5" t="inlineStr">
         <is>
           <t>2026-10-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="29" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0.2</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status column: a Candidate part's status cannot be changed by upload; Active &lt;-&gt; Inactive can be changed by upload; no part can be changed to Candidate (template, PR-03, PL-09).</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2266,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Flag A: leave blank, a new part is always Candidate. Flag E: blank or equal to the current status. Status cannot be changed by upload.</t>
+          <t xml:space="preserve">Flag A: leave blank, a new part is always Candidate. Flag E: a Candidate part keeps Candidate (blank or Candidate); an Active part can be changed to Inactive and an Inactive part to Active. No part can be changed to Candidate.</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2568,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Flag E can change only Min MAD, Pcs/Case, Max Case/Day and Effective Start Date (only while the part status is Candidate). Part No and Status cannot be changed by upload. Status is changed in the Edit part form on the screen.</t>
+          <t xml:space="preserve">Flag E can change Min MAD, Pcs/Case, Max Case/Day, Effective Start Date (only while the part status is Candidate) and Status between Active and Inactive. Part No cannot be changed. The status of a Candidate part cannot be changed by upload (it is changed in the Edit part form on the screen), and no part can be changed to Candidate.</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -3224,7 +3241,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Status: flag A is blank (always Candidate). Flag E is blank or equal to the current status.</t>
+          <t xml:space="preserve">Status: flag A is blank (a new part is always Candidate). Flag E: a Candidate part must stay Candidate (blank or Candidate); an Active or Inactive part may be Active or Inactive; Candidate is never allowed for an Active or Inactive part.</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -3234,7 +3251,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Status of a new part is always Candidate. Leave it blank. / Status cannot be changed by upload. Leave it blank or keep the current value.</t>
+          <t xml:space="preserve">Status of a new part is always Candidate. Leave it blank. / The status of a Candidate part cannot be changed by upload. / Status can only be changed between Active and Inactive.</t>
         </is>
       </c>
     </row>

--- a/FSD_Crossdock_Upload_Batch.xlsx
+++ b/FSD_Crossdock_Upload_Batch.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>New Service Part System (NSP) · Master &gt; Crossdock Master Setting · Part List Upload and Mapping per Destination Upload</t>
+          <t xml:space="preserve">Crossdock Optimization · New Service Part System (NSP) · Master &gt; Crossdock Master Setting · Part List Upload and Mapping per Destination Upload</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,11 @@
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FID Rayhan</t>
+        </is>
+      </c>
       <c r="C13" s="6" t="n"/>
     </row>
     <row r="14" ht="15.5" customHeight="1">

--- a/FSD_Crossdock_Upload_Batch.xlsx
+++ b/FSD_Crossdock_Upload_Batch.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crossdock Optimization · New Service Part System (NSP) · Master &gt; Crossdock Master Setting · Part List Upload and Mapping per Destination Upload</t>
+          <t>New Service Part System (NSP) · Master &gt; Crossdock Master Setting · Part List Upload and Mapping per Destination Upload</t>
         </is>
       </c>
     </row>
@@ -667,11 +667,7 @@
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FID Rayhan</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="6" t="n"/>
     </row>
     <row r="14" ht="15.5" customHeight="1">
